--- a/Temp.xlsx
+++ b/Temp.xlsx
@@ -999,10 +999,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RatesTable" displayName="RatesTable" ref="A1:H361" headerRowCount="1">
   <autoFilter ref="A1:H361"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="Application Type"/>
-    <tableColumn id="2" name="Application Name"/>
-    <tableColumn id="3" name="Testing Type"/>
-    <tableColumn id="4" name="Sub-Type"/>
+    <tableColumn id="1" name="ApplicationType"/>
+    <tableColumn id="2" name="ApplicationName"/>
+    <tableColumn id="3" name="TestingType"/>
+    <tableColumn id="4" name="SubType"/>
     <tableColumn id="5" name="Size"/>
     <tableColumn id="6" name="Hours"/>
     <tableColumn id="7" name="Unit"/>
@@ -1016,10 +1016,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TaskDistributionTable" displayName="TaskDistributionTable" ref="A1:P73" headerRowCount="1">
   <autoFilter ref="A1:P73"/>
   <tableColumns count="16">
-    <tableColumn id="1" name="Application Type"/>
-    <tableColumn id="2" name="Application Name"/>
-    <tableColumn id="3" name="Testing Type"/>
-    <tableColumn id="4" name="Sub-Type"/>
+    <tableColumn id="1" name="ApplicationType"/>
+    <tableColumn id="2" name="ApplicationName"/>
+    <tableColumn id="3" name="TestingType"/>
+    <tableColumn id="4" name="SubType"/>
     <tableColumn id="5" name="SP_1_2"/>
     <tableColumn id="6" name="SP_3_5"/>
     <tableColumn id="7" name="SP_8"/>
@@ -1030,8 +1030,8 @@
     <tableColumn id="12" name="Mix_M"/>
     <tableColumn id="13" name="Mix_L"/>
     <tableColumn id="14" name="Mix_XL"/>
-    <tableColumn id="15" name="Default_Reuse"/>
-    <tableColumn id="16" name="Default_AI_Efficiency"/>
+    <tableColumn id="15" name="DefaultReuse"/>
+    <tableColumn id="16" name="DefaultAIEfficiency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1041,10 +1041,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ApplicationTypesTable" displayName="ApplicationTypesTable" ref="A2:D6" headerRowCount="1">
   <autoFilter ref="A2:D6"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="Application Type ID"/>
-    <tableColumn id="2" name="Application Type"/>
-    <tableColumn id="3" name="Active (Y/N)"/>
-    <tableColumn id="4" name="Display Order"/>
+    <tableColumn id="1" name="ApplicationTypeID"/>
+    <tableColumn id="2" name="ApplicationType"/>
+    <tableColumn id="3" name="ActiveYN"/>
+    <tableColumn id="4" name="DisplayOrder"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1054,10 +1054,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="MethodologiesTable" displayName="MethodologiesTable" ref="F2:I4" headerRowCount="1">
   <autoFilter ref="F2:I4"/>
   <tableColumns count="4">
-    <tableColumn id="6" name="Methodology ID"/>
+    <tableColumn id="6" name="MethodologyID"/>
     <tableColumn id="7" name="Methodology"/>
-    <tableColumn id="8" name="Active (Y/N)"/>
-    <tableColumn id="9" name="Display Order"/>
+    <tableColumn id="8" name="ActiveYN"/>
+    <tableColumn id="9" name="DisplayOrder"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1067,10 +1067,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="ApplicationsTable" displayName="ApplicationsTable" ref="K2:N8" headerRowCount="1">
   <autoFilter ref="K2:N8"/>
   <tableColumns count="4">
-    <tableColumn id="11" name="Application Type"/>
-    <tableColumn id="12" name="Application Name"/>
-    <tableColumn id="13" name="Active (Y/N)"/>
-    <tableColumn id="14" name="Display Order"/>
+    <tableColumn id="11" name="ApplicationType"/>
+    <tableColumn id="12" name="ApplicationName"/>
+    <tableColumn id="13" name="ActiveYN"/>
+    <tableColumn id="14" name="DisplayOrder"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1505,24 +1505,24 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="40">
-      <c r="A1" s="176" t="inlineStr">
-        <is>
-          <t>Application Type</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ApplicationType</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Application Name</t>
+          <t>ApplicationName</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Testing Type</t>
+          <t>TestingType</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Sub-Type</t>
+          <t>SubType</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -14738,22 +14738,22 @@
     <row r="1" ht="25" customHeight="1" s="40">
       <c r="A1" s="176" t="inlineStr">
         <is>
-          <t>Application Type</t>
+          <t>ApplicationType</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Application Name</t>
+          <t>ApplicationName</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Testing Type</t>
+          <t>TestingType</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Sub-Type</t>
+          <t>SubType</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -14808,12 +14808,12 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Default_Reuse</t>
+          <t>DefaultReuse</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Default_AI_Efficiency</t>
+          <t>DefaultAIEfficiency</t>
         </is>
       </c>
     </row>
@@ -19041,27 +19041,27 @@
     <row r="2">
       <c r="A2" s="176" t="inlineStr">
         <is>
-          <t>Application Type ID</t>
+          <t>ApplicationTypeID</t>
         </is>
       </c>
       <c r="B2" s="176" t="inlineStr">
         <is>
-          <t>Application Type</t>
+          <t>ApplicationType</t>
         </is>
       </c>
       <c r="C2" s="176" t="inlineStr">
         <is>
-          <t>Active (Y/N)</t>
+          <t>ActiveYN</t>
         </is>
       </c>
       <c r="D2" s="176" t="inlineStr">
         <is>
-          <t>Display Order</t>
+          <t>DisplayOrder</t>
         </is>
       </c>
       <c r="F2" s="176" t="inlineStr">
         <is>
-          <t>Methodology ID</t>
+          <t>MethodologyID</t>
         </is>
       </c>
       <c r="G2" s="176" t="inlineStr">
@@ -19071,32 +19071,32 @@
       </c>
       <c r="H2" s="176" t="inlineStr">
         <is>
-          <t>Active (Y/N)</t>
+          <t>ActiveYN</t>
         </is>
       </c>
       <c r="I2" s="176" t="inlineStr">
         <is>
-          <t>Display Order</t>
+          <t>DisplayOrder</t>
         </is>
       </c>
       <c r="K2" s="176" t="inlineStr">
         <is>
-          <t>Application Type</t>
+          <t>ApplicationType</t>
         </is>
       </c>
       <c r="L2" s="176" t="inlineStr">
         <is>
-          <t>Application Name</t>
+          <t>ApplicationName</t>
         </is>
       </c>
       <c r="M2" s="176" t="inlineStr">
         <is>
-          <t>Active (Y/N)</t>
+          <t>ActiveYN</t>
         </is>
       </c>
       <c r="N2" s="176" t="inlineStr">
         <is>
-          <t>Display Order</t>
+          <t>DisplayOrder</t>
         </is>
       </c>
     </row>

--- a/Temp.xlsx
+++ b/Temp.xlsx
@@ -980,7 +980,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RatesTable" displayName="RatesTable" ref="A1:K361" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RatesTable" displayName="RatesTable" ref="A1:K421" headerRowCount="1">
   <autoFilter ref="A1:H361"/>
   <tableColumns count="11">
     <tableColumn id="1" name="ApplicationType"/>
@@ -1000,7 +1000,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TaskDistributionTable" displayName="TaskDistributionTable" ref="A1:P73" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TaskDistributionTable" displayName="TaskDistributionTable" ref="A1:P85" headerRowCount="1">
   <autoFilter ref="A1:P73"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ApplicationType"/>
@@ -1244,7 +1244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K361"/>
+  <dimension ref="A1:K421"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.39999961853027"/>
   <cols>
     <col width="18" customWidth="1" style="40" min="1" max="3"/>
@@ -17154,6 +17154,2946 @@
       <c r="J361" t="inlineStr">
         <is>
           <t>Hours/Scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H362" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I362" t="n">
+        <v>3</v>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G363" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H363" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I363" t="n">
+        <v>6</v>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G364" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H364" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I364" t="n">
+        <v>12</v>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F365" t="n">
+        <v>4</v>
+      </c>
+      <c r="G365" t="n">
+        <v>2</v>
+      </c>
+      <c r="H365" t="n">
+        <v>14</v>
+      </c>
+      <c r="I365" t="n">
+        <v>20</v>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F366" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G366" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H366" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I366" t="n">
+        <v>32</v>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G367" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H367" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I367" t="n">
+        <v>2</v>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F368" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G368" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H368" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I368" t="n">
+        <v>4</v>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F369" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G369" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H369" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I369" t="n">
+        <v>8</v>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G370" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H370" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I370" t="n">
+        <v>14</v>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G371" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H371" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I371" t="n">
+        <v>24</v>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F372" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G372" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H372" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I372" t="n">
+        <v>3</v>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G373" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H373" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I373" t="n">
+        <v>6</v>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F374" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G374" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H374" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I374" t="n">
+        <v>12</v>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>4</v>
+      </c>
+      <c r="G375" t="n">
+        <v>2</v>
+      </c>
+      <c r="H375" t="n">
+        <v>14</v>
+      </c>
+      <c r="I375" t="n">
+        <v>20</v>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G376" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H376" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I376" t="n">
+        <v>32</v>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G377" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H377" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I377" t="n">
+        <v>2</v>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G378" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H378" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I378" t="n">
+        <v>4</v>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G379" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H379" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I379" t="n">
+        <v>8</v>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G380" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H380" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I380" t="n">
+        <v>14</v>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G381" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H381" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I381" t="n">
+        <v>24</v>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G382" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H382" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I382" t="n">
+        <v>3</v>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G383" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H383" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I383" t="n">
+        <v>6</v>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G384" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H384" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I384" t="n">
+        <v>12</v>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>4</v>
+      </c>
+      <c r="G385" t="n">
+        <v>2</v>
+      </c>
+      <c r="H385" t="n">
+        <v>14</v>
+      </c>
+      <c r="I385" t="n">
+        <v>20</v>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G386" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H386" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I386" t="n">
+        <v>32</v>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G387" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H387" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I387" t="n">
+        <v>2</v>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G388" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H388" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I388" t="n">
+        <v>4</v>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G389" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H389" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I389" t="n">
+        <v>8</v>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G390" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H390" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I390" t="n">
+        <v>14</v>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G391" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H391" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I391" t="n">
+        <v>24</v>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G392" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H392" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I392" t="n">
+        <v>3</v>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G393" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H393" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I393" t="n">
+        <v>6</v>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G394" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H394" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I394" t="n">
+        <v>12</v>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>4</v>
+      </c>
+      <c r="G395" t="n">
+        <v>2</v>
+      </c>
+      <c r="H395" t="n">
+        <v>14</v>
+      </c>
+      <c r="I395" t="n">
+        <v>20</v>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G396" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H396" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I396" t="n">
+        <v>32</v>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G397" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H397" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I397" t="n">
+        <v>2</v>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G398" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H398" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I398" t="n">
+        <v>4</v>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G399" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H399" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I399" t="n">
+        <v>8</v>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G400" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H400" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I400" t="n">
+        <v>14</v>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G401" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H401" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I401" t="n">
+        <v>24</v>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G402" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H402" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I402" t="n">
+        <v>3</v>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G403" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H403" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I403" t="n">
+        <v>6</v>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G404" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H404" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I404" t="n">
+        <v>12</v>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>4</v>
+      </c>
+      <c r="G405" t="n">
+        <v>2</v>
+      </c>
+      <c r="H405" t="n">
+        <v>14</v>
+      </c>
+      <c r="I405" t="n">
+        <v>20</v>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G406" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H406" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I406" t="n">
+        <v>32</v>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G407" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H407" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I407" t="n">
+        <v>2</v>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G408" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H408" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I408" t="n">
+        <v>4</v>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G409" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H409" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I409" t="n">
+        <v>8</v>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G410" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H410" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I410" t="n">
+        <v>14</v>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G411" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H411" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I411" t="n">
+        <v>24</v>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G412" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H412" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I412" t="n">
+        <v>3</v>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F413" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G413" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H413" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I413" t="n">
+        <v>6</v>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F414" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H414" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I414" t="n">
+        <v>12</v>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F415" t="n">
+        <v>4</v>
+      </c>
+      <c r="G415" t="n">
+        <v>2</v>
+      </c>
+      <c r="H415" t="n">
+        <v>14</v>
+      </c>
+      <c r="I415" t="n">
+        <v>20</v>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F416" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G416" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H416" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I416" t="n">
+        <v>32</v>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F417" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G417" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H417" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I417" t="n">
+        <v>2</v>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G418" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H418" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I418" t="n">
+        <v>4</v>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F419" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G419" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H419" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I419" t="n">
+        <v>8</v>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F420" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G420" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H420" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I420" t="n">
+        <v>14</v>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F421" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G421" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H421" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I421" t="n">
+        <v>24</v>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>Hours/Script</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>API automation placeholder; update as needed</t>
         </is>
       </c>
     </row>
@@ -17180,7 +20120,7 @@
     <row r="1" ht="21.75" customHeight="1" s="40">
       <c r="A1" s="166" t="inlineStr">
         <is>
-          <t>QA ESTIMATION TOOL - Configuration File Instructions</t>
+          <t>QAE Estimation Config v31 - includes API automation subtypes Selenium API and Tosca API.</t>
         </is>
       </c>
     </row>
@@ -17365,7 +20305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <cols>
     <col width="18" customWidth="1" style="40" min="1" max="1"/>
@@ -21642,6 +24582,702 @@
         <v>0</v>
       </c>
       <c r="P73" s="178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" t="n">
+        <v>5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>9</v>
+      </c>
+      <c r="I74" t="n">
+        <v>14</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>9</v>
+      </c>
+      <c r="I75" t="n">
+        <v>14</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" t="n">
+        <v>5</v>
+      </c>
+      <c r="H76" t="n">
+        <v>9</v>
+      </c>
+      <c r="I76" t="n">
+        <v>14</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Non-SAP ERP</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5</v>
+      </c>
+      <c r="H77" t="n">
+        <v>9</v>
+      </c>
+      <c r="I77" t="n">
+        <v>14</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" t="n">
+        <v>5</v>
+      </c>
+      <c r="H78" t="n">
+        <v>9</v>
+      </c>
+      <c r="I78" t="n">
+        <v>14</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>9</v>
+      </c>
+      <c r="I79" t="n">
+        <v>14</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" t="n">
+        <v>5</v>
+      </c>
+      <c r="H80" t="n">
+        <v>9</v>
+      </c>
+      <c r="I80" t="n">
+        <v>14</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>S/4 Hana</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>9</v>
+      </c>
+      <c r="I81" t="n">
+        <v>14</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5</v>
+      </c>
+      <c r="H82" t="n">
+        <v>9</v>
+      </c>
+      <c r="I82" t="n">
+        <v>14</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" t="n">
+        <v>5</v>
+      </c>
+      <c r="H83" t="n">
+        <v>9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>14</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Selenium API</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" t="n">
+        <v>5</v>
+      </c>
+      <c r="H84" t="n">
+        <v>9</v>
+      </c>
+      <c r="I84" t="n">
+        <v>14</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Tosca API</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3</v>
+      </c>
+      <c r="G85" t="n">
+        <v>5</v>
+      </c>
+      <c r="H85" t="n">
+        <v>9</v>
+      </c>
+      <c r="I85" t="n">
+        <v>14</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Temp.xlsx
+++ b/Temp.xlsx
@@ -256,6 +256,17 @@
     <tableColumn id="24" name="DisplayOrder"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ConfigSettingsTable" displayName="ConfigSettingsTable" ref="Z2:AA4" totalsRowShown="0">
+  <autoFilter ref="Z2:AA4"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="SettingKey"/>
+    <tableColumn id="2" name="SettingValue"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -32874,12 +32885,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32898,6 +32909,11 @@
           <t>Automation Tools</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Config Settings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -33000,6 +33016,16 @@
           <t>DisplayOrder</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>SettingKey</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>SettingValue</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33087,6 +33113,16 @@
       <c r="X3" t="n">
         <v>1</v>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ConfigVersion</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>v82</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33179,6 +33215,16 @@
       <c r="X4" t="n">
         <v>2</v>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>ConfigDate</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33559,12 +33605,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="5">
+  <tableParts count="6">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Temp.xlsx
+++ b/Temp.xlsx
@@ -23612,9 +23612,7 @@
       <x:c r="N4" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O4" s="2" t="str">
-        <x:v>Agile</x:v>
-      </x:c>
+      <x:c r="O4" s="2"/>
       <x:c r="P4" s="2" t="str">
         <x:v>StoryPoints</x:v>
       </x:c>
@@ -23677,8 +23675,10 @@
       <x:c r="P5" s="2" t="str">
         <x:v>TestConditions</x:v>
       </x:c>
-      <x:c r="Q5" s="2" t="str">
-        <x:v>Replace</x:v>
+      <x:c r="Q5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Inherit</x:t>
+        </x:is>
       </x:c>
       <x:c r="U5" s="1" t="inlineStr">
         <x:is>
@@ -23736,8 +23736,10 @@
       <x:c r="P6" s="2" t="str">
         <x:v>TestConditions</x:v>
       </x:c>
-      <x:c r="Q6" s="2" t="str">
-        <x:v>Replace</x:v>
+      <x:c r="Q6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Inherit</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
@@ -23759,8 +23761,10 @@
       <x:c r="P7" s="2" t="str">
         <x:v>TestConditions</x:v>
       </x:c>
-      <x:c r="Q7" s="2" t="str">
-        <x:v>Replace</x:v>
+      <x:c r="Q7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Inherit</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
@@ -23782,8 +23786,10 @@
       <x:c r="P8" s="2" t="str">
         <x:v>TestConditions</x:v>
       </x:c>
-      <x:c r="Q8" s="2" t="str">
-        <x:v>Replace</x:v>
+      <x:c r="Q8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Inherit</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
@@ -23805,8 +23811,10 @@
       <x:c r="P9" s="2" t="str">
         <x:v>TestConditions</x:v>
       </x:c>
-      <x:c r="Q9" s="2" t="str">
-        <x:v>Replace</x:v>
+      <x:c r="Q9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Inherit</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
@@ -23828,8 +23836,10 @@
       <x:c r="P10" s="2" t="str">
         <x:v>TestConditions</x:v>
       </x:c>
-      <x:c r="Q10" s="2" t="str">
-        <x:v>Replace</x:v>
+      <x:c r="Q10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Inherit</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
@@ -23851,8 +23861,10 @@
       <x:c r="P11" s="2" t="str">
         <x:v>TestConditions</x:v>
       </x:c>
-      <x:c r="Q11" s="2" t="str">
-        <x:v>Replace</x:v>
+      <x:c r="Q11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Inherit</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
@@ -23874,8 +23886,10 @@
       <x:c r="P12" s="2" t="str">
         <x:v>TestConditions</x:v>
       </x:c>
-      <x:c r="Q12" s="2" t="str">
-        <x:v>Replace</x:v>
+      <x:c r="Q12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Inherit</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
